--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_27.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_27.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>PerfectionismRating</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>InformationLevel</t>
+          <t>IQ</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-1.028866282144693</v>
+        <v>0.7761411145678213</v>
       </c>
       <c r="C2">
-        <v>0.239047414311673</v>
+        <v>0.9475287377169854</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.9349498591618306</v>
+        <v>1.694153944062811</v>
       </c>
       <c r="C3">
-        <v>-0.457919874337772</v>
+        <v>1.027315590022443</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.4165639729437851</v>
+        <v>1.010357363588753</v>
       </c>
       <c r="C4">
-        <v>1.070849911026626</v>
+        <v>-0.5021663107968037</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3525266318269367</v>
+        <v>-0.2569841646254815</v>
       </c>
       <c r="C5">
-        <v>0.724723865740729</v>
+        <v>0.4971710474477247</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2823829022485655</v>
+        <v>-0.1027466456441216</v>
       </c>
       <c r="C6">
-        <v>-0.3218178286311779</v>
+        <v>-0.8070766342454416</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.442524340898663</v>
+        <v>-0.752195999753034</v>
       </c>
       <c r="C7">
-        <v>0.2467790308550482</v>
+        <v>-0.5597068305494366</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.3449069827628549</v>
+        <v>1.261987526477249</v>
       </c>
       <c r="C8">
-        <v>1.12795288889123</v>
+        <v>0.382639010653094</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.9769239812439195</v>
+        <v>0.07145836815595788</v>
       </c>
       <c r="C9">
-        <v>0.3756308340501382</v>
+        <v>-1.786492003949145</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.5244445730722699</v>
+        <v>-0.1538694197294364</v>
       </c>
       <c r="C10">
-        <v>0.6561448099884591</v>
+        <v>-0.1982855355997684</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.08851822465367727</v>
+        <v>1.006393907119305</v>
       </c>
       <c r="C11">
-        <v>-1.397318414829316</v>
+        <v>1.579541165720867</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.268585040394027</v>
+        <v>0.06001925476327633</v>
       </c>
       <c r="C12">
-        <v>1.084852099047869</v>
+        <v>-0.2740113569837415</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.5306201330232032</v>
+        <v>-0.7207513396427708</v>
       </c>
       <c r="C13">
-        <v>0.372264341492418</v>
+        <v>-0.6328116890066267</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.04012539127162</v>
+        <v>0.1666016594301286</v>
       </c>
       <c r="C14">
-        <v>0.8797094745096752</v>
+        <v>1.520110932479974</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-1.576265957229084</v>
+        <v>2.178192354399468</v>
       </c>
       <c r="C15">
-        <v>-0.731813753274647</v>
+        <v>1.595416509741674</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.9481331442285436</v>
+        <v>-0.6641874415495198</v>
       </c>
       <c r="C16">
-        <v>-0.3875491197304556</v>
+        <v>-0.6450083341934607</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-1.617878102338297</v>
+        <v>0.0007170375324058833</v>
       </c>
       <c r="C17">
-        <v>-1.425872687757635</v>
+        <v>-0.005985635418887081</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.331634051656958</v>
+        <v>-1.33283691218376</v>
       </c>
       <c r="C18">
-        <v>-1.024675168354184</v>
+        <v>-1.360532916233817</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.3429267805588</v>
+        <v>-1.206046347615504</v>
       </c>
       <c r="C19">
-        <v>0.5559291761286422</v>
+        <v>0.07100393016434658</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.5113515981705781</v>
+        <v>0.7703940555476977</v>
       </c>
       <c r="C20">
-        <v>-0.8638853338673944</v>
+        <v>-1.002356562126913</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-1.125023157380381</v>
+        <v>-1.318946735903359</v>
       </c>
       <c r="C21">
-        <v>-1.570266619965255</v>
+        <v>-1.39504817116862</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.2730890835278386</v>
+        <v>-1.281625264661572</v>
       </c>
       <c r="C22">
-        <v>-0.6822729430189053</v>
+        <v>-1.469255257667268</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.292963371238268</v>
+        <v>0.9270278219031544</v>
       </c>
       <c r="C23">
-        <v>0.8185736785216091</v>
+        <v>1.87658162829686</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.5665736402659518</v>
+        <v>0.1909300355269367</v>
       </c>
       <c r="C24">
-        <v>0.7822898074304904</v>
+        <v>0.9376657046513809</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.9668898201275189</v>
+        <v>1.163260011987185</v>
       </c>
       <c r="C25">
-        <v>1.415732445036832</v>
+        <v>1.040021314651784</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.04134367068482065</v>
+        <v>-2.314602934653303</v>
       </c>
       <c r="C26">
-        <v>-0.1241474902970979</v>
+        <v>-1.02341386332796</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.3672533940322762</v>
+        <v>0.5525381799714988</v>
       </c>
       <c r="C27">
-        <v>0.8071405522763453</v>
+        <v>1.759113327840251</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.4925371678956819</v>
+        <v>0.5102651332880326</v>
       </c>
       <c r="C28">
-        <v>1.173293164821441</v>
+        <v>0.9512423662906805</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.1159712216995618</v>
+        <v>-0.9056948294486882</v>
       </c>
       <c r="C29">
-        <v>-0.1454567377093986</v>
+        <v>-0.2871185897031096</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>1.850976262845236</v>
+        <v>-1.816877607840125</v>
       </c>
       <c r="C30">
-        <v>0.6486349709240408</v>
+        <v>-0.1946072227666413</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>1.20897645667454</v>
+        <v>0.4994052341562897</v>
       </c>
       <c r="C31">
-        <v>-0.1855312668251453</v>
+        <v>-1.653668717677047</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>1.771417985097398</v>
+        <v>0.9113856597457437</v>
       </c>
       <c r="C32">
-        <v>0.921310385039428</v>
+        <v>0.9399268731250788</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.3544177798824402</v>
+        <v>-0.3130783472142192</v>
       </c>
       <c r="C33">
-        <v>-0.8439600519896263</v>
+        <v>-0.2306485739386746</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.4232559296741059</v>
+        <v>-1.551730427292404</v>
       </c>
       <c r="C34">
-        <v>0.41911756985732</v>
+        <v>0.09940895082939771</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.9513602866319548</v>
+        <v>0.4902935093331542</v>
       </c>
       <c r="C35">
-        <v>1.316539127124145</v>
+        <v>-1.176136069937545</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.7991137762494901</v>
+        <v>-0.5899702973089429</v>
       </c>
       <c r="C36">
-        <v>0.9831031628433619</v>
+        <v>-1.263502435005715</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>1.127453145611004</v>
+        <v>1.473202312037786</v>
       </c>
       <c r="C37">
-        <v>0.2676606301640853</v>
+        <v>0.3409523475422019</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>2.360511750747954</v>
+        <v>-0.1226860011861053</v>
       </c>
       <c r="C38">
-        <v>1.992713965477349</v>
+        <v>0.6672735025330104</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>1.059612267675819</v>
+        <v>2.18619866625043</v>
       </c>
       <c r="C39">
-        <v>1.803220505288752</v>
+        <v>1.374746066943231</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.39134583320141</v>
+        <v>-0.8819971873701297</v>
       </c>
       <c r="C40">
-        <v>-0.3017842541055064</v>
+        <v>-1.612173757671651</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>2.813484967568222</v>
+        <v>-1.385500270776028</v>
       </c>
       <c r="C41">
-        <v>-2.327382857177938</v>
+        <v>-0.3736883613561783</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-1.2795300536365</v>
+        <v>1.521306666715294</v>
       </c>
       <c r="C42">
-        <v>-1.116467557124773</v>
+        <v>0.1370501356325038</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>1.311406655628139</v>
+        <v>-0.3680324276970069</v>
       </c>
       <c r="C43">
-        <v>1.34554209934066</v>
+        <v>2.170206261812757</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.576990659067094</v>
+        <v>-1.696799572048553</v>
       </c>
       <c r="C44">
-        <v>2.084672373408177</v>
+        <v>-1.207825650207878</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.06466734410827159</v>
+        <v>-1.338707812604071</v>
       </c>
       <c r="C45">
-        <v>0.8964315017328802</v>
+        <v>0.5506767469353214</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.8941190793083906</v>
+        <v>2.681918097018036</v>
       </c>
       <c r="C46">
-        <v>-0.8784194433222223</v>
+        <v>1.572323839499206</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.020525505049192</v>
+        <v>0.1663474348721198</v>
       </c>
       <c r="C47">
-        <v>-1.753083193981432</v>
+        <v>-0.09604147880635426</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.2829021161619092</v>
+        <v>-0.3581596493117931</v>
       </c>
       <c r="C48">
-        <v>0.03661293213110639</v>
+        <v>-0.1576586226063768</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-1.713647501173896</v>
+        <v>0.8724104047510491</v>
       </c>
       <c r="C49">
-        <v>-0.840287239725513</v>
+        <v>0.3301560266960326</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.4022069374167172</v>
+        <v>-0.3673104486598633</v>
       </c>
       <c r="C50">
-        <v>1.930334039804786</v>
+        <v>1.517813171675626</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.721833339982299</v>
+        <v>-0.569043709900674</v>
       </c>
       <c r="C51">
-        <v>1.094089434713979</v>
+        <v>-0.8356769422813841</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.09236686024172519</v>
+        <v>0.238418973510937</v>
       </c>
       <c r="C52">
-        <v>-0.1941615973817139</v>
+        <v>-0.656578171859312</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.3065032925883743</v>
+        <v>0.09751520824650492</v>
       </c>
       <c r="C53">
-        <v>-0.8128826236211624</v>
+        <v>0.3602227212781535</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>1.125033474145598</v>
+        <v>1.840603448311239</v>
       </c>
       <c r="C54">
-        <v>0.5771565654832378</v>
+        <v>0.5264639505346722</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.5782971841008474</v>
+        <v>0.2246804530676574</v>
       </c>
       <c r="C55">
-        <v>1.291632599594164</v>
+        <v>-0.5202293413025111</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.3056122891580543</v>
+        <v>-0.5693554757789362</v>
       </c>
       <c r="C56">
-        <v>-0.6928893063752091</v>
+        <v>0.3610846200161616</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>-0.1182274973211102</v>
+        <v>-2.218874869378167</v>
       </c>
       <c r="C57">
-        <v>1.168675451093497</v>
+        <v>-0.1322624319733998</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-1.679447763659122</v>
+        <v>-0.7359524783873249</v>
       </c>
       <c r="C58">
-        <v>0.04887476871606966</v>
+        <v>-0.3734453343795573</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>-0.0385110879226549</v>
+        <v>2.723395641025157</v>
       </c>
       <c r="C59">
-        <v>-0.5236289958285739</v>
+        <v>-0.364461764603762</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>1.360630267125741</v>
+        <v>1.613468112231811</v>
       </c>
       <c r="C60">
-        <v>0.2464766782757395</v>
+        <v>0.6558785055994644</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>-0.1353301188672176</v>
+        <v>1.48231095603406</v>
       </c>
       <c r="C61">
-        <v>0.8520236921218945</v>
+        <v>0.3207846053704033</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>-0.8380712133388075</v>
+        <v>-1.186755713475802</v>
       </c>
       <c r="C62">
-        <v>-0.5838607127872832</v>
+        <v>-1.770878772574789</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>-0.03842425124318857</v>
+        <v>-1.920109774250754</v>
       </c>
       <c r="C63">
-        <v>0.9528271365326459</v>
+        <v>-0.01181639194662898</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>1.202410972359018</v>
+        <v>1.220506856477768</v>
       </c>
       <c r="C64">
-        <v>1.081200101720104</v>
+        <v>0.8109144547757252</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.2510043945601664</v>
+        <v>-2.857043173260057</v>
       </c>
       <c r="C65">
-        <v>2.408302145103305</v>
+        <v>-1.25232464659263</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.3194548969678278</v>
+        <v>0.6741882883783751</v>
       </c>
       <c r="C66">
-        <v>-0.3229657495400727</v>
+        <v>-1.576295190038476</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.02890769414947808</v>
+        <v>-0.146453367302996</v>
       </c>
       <c r="C67">
-        <v>-1.281658037331151</v>
+        <v>0.8688151158907166</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>0.6904678375348247</v>
+        <v>0.4916553117364343</v>
       </c>
       <c r="C68">
-        <v>-0.318959067737021</v>
+        <v>1.944592249628537</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.8079816144836847</v>
+        <v>2.054343853141319</v>
       </c>
       <c r="C69">
-        <v>0.9983926868638977</v>
+        <v>0.9584756790396568</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-1.527826020915692</v>
+        <v>1.541851622385177</v>
       </c>
       <c r="C70">
-        <v>-1.092314134176592</v>
+        <v>1.163889961778702</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.9355547954567711</v>
+        <v>-1.510450948220036</v>
       </c>
       <c r="C71">
-        <v>-0.971059513046497</v>
+        <v>-0.5916161500700287</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-1.473819672353518</v>
+        <v>0.8840605110061566</v>
       </c>
       <c r="C72">
-        <v>-1.149352212123705</v>
+        <v>0.4728298798086314</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-1.001325639862015</v>
+        <v>0.1783007261626333</v>
       </c>
       <c r="C73">
-        <v>-0.02943585169068286</v>
+        <v>-0.1552852887686518</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-0.7441276317202774</v>
+        <v>3.173064926824353</v>
       </c>
       <c r="C74">
-        <v>0.3169333363539324</v>
+        <v>2.2890155509487</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-1.049699264008925</v>
+        <v>0.7633521882305576</v>
       </c>
       <c r="C75">
-        <v>-1.347637076976578</v>
+        <v>0.8007806706297209</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>1.265842547471631</v>
+        <v>-2.076014104689374</v>
       </c>
       <c r="C76">
-        <v>0.4807615571770167</v>
+        <v>-0.101892019101393</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-0.8522486603660905</v>
+        <v>1.435002639272598</v>
       </c>
       <c r="C77">
-        <v>1.000377075746994</v>
+        <v>0.4238442067065452</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>-0.1062414475927154</v>
+        <v>0.003727038144508776</v>
       </c>
       <c r="C78">
-        <v>-0.3583404512853309</v>
+        <v>0.9065493864058362</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>1.052039074408365</v>
+        <v>0.2318176483795502</v>
       </c>
       <c r="C79">
-        <v>0.7252307786497835</v>
+        <v>-0.09955223983934097</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.09424977619947378</v>
+        <v>-0.2770224843017449</v>
       </c>
       <c r="C80">
-        <v>0.7094564304069479</v>
+        <v>-0.8281423839003973</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-0.217977021342391</v>
+        <v>0.2129729525811258</v>
       </c>
       <c r="C81">
-        <v>-0.7166763893792006</v>
+        <v>-0.3006641046202053</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.534264920987918</v>
+        <v>-0.340746031704794</v>
       </c>
       <c r="C82">
-        <v>-0.9190176790810325</v>
+        <v>-0.09356832260338398</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.05270912091613168</v>
+        <v>-1.764710978640671</v>
       </c>
       <c r="C83">
-        <v>-0.1433157414353979</v>
+        <v>-0.5575001222041776</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.6839053171918635</v>
+        <v>-1.18681296557444</v>
       </c>
       <c r="C84">
-        <v>-0.7937176349462665</v>
+        <v>0.3089418384841142</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.1912610159593776</v>
+        <v>-0.4657627071470414</v>
       </c>
       <c r="C85">
-        <v>0.943267080658448</v>
+        <v>0.5812374837884063</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.2168184250658039</v>
+        <v>-0.4821061292378677</v>
       </c>
       <c r="C86">
-        <v>-1.5740869361612</v>
+        <v>1.103001856323576</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>-0.9202677827770724</v>
+        <v>1.441785564374163</v>
       </c>
       <c r="C87">
-        <v>-0.7734403413644291</v>
+        <v>-0.1824557688368207</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-0.3844841768549688</v>
+        <v>0.1222749895281864</v>
       </c>
       <c r="C88">
-        <v>0.7248358248589419</v>
+        <v>1.146059506093939</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>-1.361599730687783</v>
+        <v>2.506013902505481</v>
       </c>
       <c r="C89">
-        <v>-0.4291086686573469</v>
+        <v>1.397371489006151</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.7880666156009142</v>
+        <v>0.5696353903250885</v>
       </c>
       <c r="C90">
-        <v>0.0292414917959769</v>
+        <v>0.9209220648838288</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.6821525782719072</v>
+        <v>0.9255882763415683</v>
       </c>
       <c r="C91">
-        <v>0.2980621174462133</v>
+        <v>-1.548992664435075</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.4557255620959154</v>
+        <v>0.3260111971597177</v>
       </c>
       <c r="C92">
-        <v>-1.486214173400135</v>
+        <v>-0.4503032500110808</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-0.03783472461453034</v>
+        <v>-0.5113425874088461</v>
       </c>
       <c r="C93">
-        <v>-1.645182878317943</v>
+        <v>0.7175794814180376</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.4628374794043353</v>
+        <v>-0.6076018727667731</v>
       </c>
       <c r="C94">
-        <v>1.289500648671882</v>
+        <v>-0.6210498234185233</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.7394806225721691</v>
+        <v>1.190233494524825</v>
       </c>
       <c r="C95">
-        <v>-0.5382545652572523</v>
+        <v>2.813066651692748</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>-0.6989429235712855</v>
+        <v>-0.3646184974369271</v>
       </c>
       <c r="C96">
-        <v>0.371384818047688</v>
+        <v>-0.155078549105186</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.5605022355645536</v>
+        <v>-0.1851282058499805</v>
       </c>
       <c r="C97">
-        <v>-0.8160970516226717</v>
+        <v>-0.6468724510818534</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.636202002754246</v>
+        <v>0.6184087501689483</v>
       </c>
       <c r="C98">
-        <v>-0.3317049576190619</v>
+        <v>0.3889587980510997</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-1.223955746560108</v>
+        <v>-1.711782325675158</v>
       </c>
       <c r="C99">
-        <v>0.2568535082192399</v>
+        <v>-1.149072809230572</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>1.126246153598129</v>
+        <v>-0.387152333866964</v>
       </c>
       <c r="C100">
-        <v>1.636456150213967</v>
+        <v>-1.032251774455503</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>1.106572863845612</v>
+        <v>0.6005404131221734</v>
       </c>
       <c r="C101">
-        <v>-0.6031823545930843</v>
+        <v>0.3431965940421496</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.1200178864352677</v>
+        <v>-0.827865392559166</v>
       </c>
       <c r="C102">
-        <v>0.005420214976249289</v>
+        <v>0.8324435147257405</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>-0.2242807908959495</v>
+        <v>1.956147998509871</v>
       </c>
       <c r="C103">
-        <v>0.58601823299103</v>
+        <v>-0.4474690035616301</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>-0.7161910249378328</v>
+        <v>-2.064966909295861</v>
       </c>
       <c r="C104">
-        <v>-0.4229842205047083</v>
+        <v>-1.643765851068243</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>2.818666149357482</v>
+        <v>0.7561702043786173</v>
       </c>
       <c r="C105">
-        <v>1.516332591180855</v>
+        <v>1.485986000396891</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.3079583091678789</v>
+        <v>0.6319299306027599</v>
       </c>
       <c r="C106">
-        <v>-0.8641544606109768</v>
+        <v>-0.00902196410064765</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>0.7044750529791289</v>
+        <v>1.234080778168165</v>
       </c>
       <c r="C107">
-        <v>1.18689946835819</v>
+        <v>-1.603217078158237</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>1.194923502583199</v>
+        <v>1.475655678396657</v>
       </c>
       <c r="C108">
-        <v>1.457062623476864</v>
+        <v>2.999533491898719</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.6650018111521968</v>
+        <v>-0.7412960407122148</v>
       </c>
       <c r="C109">
-        <v>-0.3430872256242369</v>
+        <v>-0.3526951061010571</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.7746150401732338</v>
+        <v>1.471491380687717</v>
       </c>
       <c r="C110">
-        <v>-1.458553919846051</v>
+        <v>1.337921902124111</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>-0.2337729997859826</v>
+        <v>-0.737294803115441</v>
       </c>
       <c r="C111">
-        <v>0.3042437538558365</v>
+        <v>-0.6269941508809315</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.7068465064787759</v>
+        <v>-1.56104491771683</v>
       </c>
       <c r="C112">
-        <v>-0.1982368923165788</v>
+        <v>0.3401496660131391</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>-0.6542169600515968</v>
+        <v>-0.3486887591866542</v>
       </c>
       <c r="C113">
-        <v>1.340019453081194</v>
+        <v>-1.075890289461323</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>1.520258799755835</v>
+        <v>1.660943663606372</v>
       </c>
       <c r="C114">
-        <v>1.69823867349604</v>
+        <v>0.5629284587219041</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.319244240549379</v>
+        <v>-0.8065917277169514</v>
       </c>
       <c r="C115">
-        <v>-0.4280122729385344</v>
+        <v>-0.8018453387506411</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.4441045285376095</v>
+        <v>0.3302621269319005</v>
       </c>
       <c r="C116">
-        <v>0.1200428670820367</v>
+        <v>-0.2957076277177895</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.2375105821256908</v>
+        <v>-1.207462180823819</v>
       </c>
       <c r="C117">
-        <v>0.4696022591454795</v>
+        <v>1.178103701338249</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.0194242712888358</v>
+        <v>0.7387564029117966</v>
       </c>
       <c r="C118">
-        <v>-0.6379832862059102</v>
+        <v>0.1891365631006421</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.09359137807120757</v>
+        <v>0.5504322959715886</v>
       </c>
       <c r="C119">
-        <v>-0.864612549282551</v>
+        <v>-0.2142820215763805</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>-0.2368008600649074</v>
+        <v>0.4623067475345777</v>
       </c>
       <c r="C120">
-        <v>-1.231887579564716</v>
+        <v>-1.613567545332421</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>1.089926592615218</v>
+        <v>0.02370704032155459</v>
       </c>
       <c r="C121">
-        <v>1.120325314469751</v>
+        <v>-0.003744167772910593</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>-1.667453350340634</v>
+        <v>1.267060853256077</v>
       </c>
       <c r="C122">
-        <v>-0.01934802131105429</v>
+        <v>-0.524823899663616</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>-0.5002872757300376</v>
+        <v>0.1343417998115848</v>
       </c>
       <c r="C123">
-        <v>1.389356380813924</v>
+        <v>-0.3711003282777687</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>-1.896709326359851</v>
+        <v>0.2672594643232726</v>
       </c>
       <c r="C124">
-        <v>-0.2419729341125891</v>
+        <v>0.3448880665478806</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>1.0821194707925</v>
+        <v>1.235950851500857</v>
       </c>
       <c r="C125">
-        <v>0.8921820719975742</v>
+        <v>0.8591769910855729</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>1.454094746423225</v>
+        <v>-0.005801407175452385</v>
       </c>
       <c r="C126">
-        <v>0.3712700225378014</v>
+        <v>0.2122580763587033</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>2.235058914199743</v>
+        <v>-0.1319717472153101</v>
       </c>
       <c r="C127">
-        <v>-0.2559411624971561</v>
+        <v>0.4967156761569573</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>-2.089328651579486</v>
+        <v>-0.1648656626849901</v>
       </c>
       <c r="C128">
-        <v>-1.520426725084775</v>
+        <v>-1.462197379810854</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>-0.6736138986561983</v>
+        <v>1.63583500686606</v>
       </c>
       <c r="C129">
-        <v>1.428118557349183</v>
+        <v>-0.1431043784497413</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>1.128776124438973</v>
+        <v>0.5142007793059404</v>
       </c>
       <c r="C130">
-        <v>-1.149728499766968</v>
+        <v>-0.5628052299466973</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>2.152848781606998</v>
+        <v>-0.6609958177113598</v>
       </c>
       <c r="C131">
-        <v>0.3381344607906847</v>
+        <v>-1.132862260888066</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>-0.08655508938881262</v>
+        <v>-0.676558640415763</v>
       </c>
       <c r="C132">
-        <v>1.842666754506809</v>
+        <v>0.1805010287982277</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>-2.319701338281629</v>
+        <v>-0.4296259764633707</v>
       </c>
       <c r="C133">
-        <v>0.8247778501903845</v>
+        <v>-1.798460351244598</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>0.9743181910970081</v>
+        <v>0.2991754958591856</v>
       </c>
       <c r="C134">
-        <v>1.227626792967813</v>
+        <v>0.05589839299149202</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>-0.04775033679230228</v>
+        <v>-0.1519271379889356</v>
       </c>
       <c r="C135">
-        <v>0.1977822174277417</v>
+        <v>-0.2420828821471602</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>-0.07962525696618462</v>
+        <v>-0.1638911693806435</v>
       </c>
       <c r="C136">
-        <v>0.3077011031450072</v>
+        <v>0.002076522136253353</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>-0.6699009898716136</v>
+        <v>-0.6393905114687355</v>
       </c>
       <c r="C137">
-        <v>0.2533662388595196</v>
+        <v>0.2773669282554027</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>1.258344596241048</v>
+        <v>0.603040167192457</v>
       </c>
       <c r="C138">
-        <v>0.7449792735881084</v>
+        <v>0.4718970941395288</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>-0.7354671781513177</v>
+        <v>-0.4702553881498187</v>
       </c>
       <c r="C139">
-        <v>-0.06813591178411041</v>
+        <v>0.03329352791211485</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>0.5285347946028661</v>
+        <v>-2.437720452721458</v>
       </c>
       <c r="C140">
-        <v>0.2923984344940917</v>
+        <v>-0.7273585655900778</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.7827611578485928</v>
+        <v>0.7099155571886817</v>
       </c>
       <c r="C141">
-        <v>-1.054966314285541</v>
+        <v>-1.208127241045902</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>-1.090119732664018</v>
+        <v>-0.08575083838724043</v>
       </c>
       <c r="C142">
-        <v>-0.6692625793830509</v>
+        <v>-0.6694318614665039</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>-0.04968143999415156</v>
+        <v>0.5887977814021349</v>
       </c>
       <c r="C143">
-        <v>-1.736727961951329</v>
+        <v>-1.340991436128332</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>0.57272543733682</v>
+        <v>-0.8941302360756661</v>
       </c>
       <c r="C144">
-        <v>2.949840068085633</v>
+        <v>0.4938811512903215</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>0.8581499864003012</v>
+        <v>2.045750297151168</v>
       </c>
       <c r="C145">
-        <v>1.109755667133636</v>
+        <v>1.789118117903183</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>-0.7142039998118201</v>
+        <v>-0.2195233954873037</v>
       </c>
       <c r="C146">
-        <v>-0.9728280200257108</v>
+        <v>0.3159662573024156</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>1.077434963933014</v>
+        <v>-0.628875539902883</v>
       </c>
       <c r="C147">
-        <v>1.726136842212011</v>
+        <v>0.8911543277318353</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>-1.130776568374473</v>
+        <v>0.3477874390071315</v>
       </c>
       <c r="C148">
-        <v>-0.1038157258617714</v>
+        <v>1.204954248295779</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>-0.146125336952574</v>
+        <v>-0.1894880681555038</v>
       </c>
       <c r="C149">
-        <v>-2.196004291186724</v>
+        <v>0.08206692783727244</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>-0.4678143212021663</v>
+        <v>-1.743247804663439</v>
       </c>
       <c r="C150">
-        <v>1.333499257585373</v>
+        <v>-1.720891981645301</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>-0.7846608699803611</v>
+        <v>-1.075975768218037</v>
       </c>
       <c r="C151">
-        <v>-0.06655161195857298</v>
+        <v>1.534356185817428</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>-0.4145736794438284</v>
+        <v>-0.4207451954443185</v>
       </c>
       <c r="C152">
-        <v>-0.3511464384189653</v>
+        <v>1.403925267401527</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>-0.09749514369859009</v>
+        <v>0.6011985975282953</v>
       </c>
       <c r="C153">
-        <v>0.5764763207636013</v>
+        <v>-1.090028662227321</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>1.547585211380829</v>
+        <v>1.303783607226423</v>
       </c>
       <c r="C154">
-        <v>2.167641101164078</v>
+        <v>0.05723216268566589</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>0.9113886347677859</v>
+        <v>-0.2140399453308793</v>
       </c>
       <c r="C155">
-        <v>-1.543437693845194</v>
+        <v>-1.664557244710464</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>0.8889875515896617</v>
+        <v>-0.01552255658060619</v>
       </c>
       <c r="C156">
-        <v>-1.391580732392925</v>
+        <v>-0.410669915648365</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>1.649618094265254</v>
+        <v>0.8122178515984758</v>
       </c>
       <c r="C157">
-        <v>-0.3722432186112364</v>
+        <v>1.75652597122848</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>-0.2682798601095384</v>
+        <v>-1.06149933998083</v>
       </c>
       <c r="C158">
-        <v>0.3887908024270853</v>
+        <v>1.381905135485911</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>-1.754764724770761</v>
+        <v>-0.5925381986874447</v>
       </c>
       <c r="C159">
-        <v>-2.507878108138581</v>
+        <v>-0.3216702250712083</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>-0.1426740573588439</v>
+        <v>-0.01133653467613026</v>
       </c>
       <c r="C160">
-        <v>1.421321283259463</v>
+        <v>-1.141775841167223</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>0.1031235071858932</v>
+        <v>-2.350913215602571</v>
       </c>
       <c r="C161">
-        <v>0.667672474802476</v>
+        <v>-2.459890867678717</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>-1.581134568530361</v>
+        <v>2.19855846797681</v>
       </c>
       <c r="C162">
-        <v>-2.102087901743278</v>
+        <v>0.9285977435735706</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>0.7760423643055384</v>
+        <v>1.343453501822153</v>
       </c>
       <c r="C163">
-        <v>-0.3197921607855894</v>
+        <v>0.3564181282540181</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>0.3248521607181462</v>
+        <v>-0.854745482771636</v>
       </c>
       <c r="C164">
-        <v>0.5484421959597556</v>
+        <v>1.05475812640832</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>-0.1471387250496112</v>
+        <v>1.475852634324319</v>
       </c>
       <c r="C165">
-        <v>-0.5601286367158836</v>
+        <v>0.1410297227407699</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>0.7305168253564914</v>
+        <v>0.5241041105360834</v>
       </c>
       <c r="C166">
-        <v>1.813039018836494</v>
+        <v>0.6540472850517678</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>-0.2183741980545192</v>
+        <v>1.954634074762004</v>
       </c>
       <c r="C167">
-        <v>-0.4324770331765428</v>
+        <v>-0.1099081505017537</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>-0.2173029661891083</v>
+        <v>1.050808902360421</v>
       </c>
       <c r="C168">
-        <v>1.261171199771896</v>
+        <v>0.3016092817382681</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>1.045604535382919</v>
+        <v>-0.8020662060548205</v>
       </c>
       <c r="C169">
-        <v>-0.1674544733229058</v>
+        <v>-0.688032599067067</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>1.688791960647799</v>
+        <v>0.00715154756914189</v>
       </c>
       <c r="C170">
-        <v>1.596429869898639</v>
+        <v>-0.1171986908186844</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>1.924234153623639</v>
+        <v>0.6573157476697207</v>
       </c>
       <c r="C171">
-        <v>0.5682727409548136</v>
+        <v>-0.4428709727810821</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>1.010607736607244</v>
+        <v>-1.325369893602279</v>
       </c>
       <c r="C172">
-        <v>1.427906138929512</v>
+        <v>-1.907951464917757</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>-0.2576128006501562</v>
+        <v>0.6959399313302305</v>
       </c>
       <c r="C173">
-        <v>0.344955692149389</v>
+        <v>-1.363719662425864</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>-0.3066292433696666</v>
+        <v>-0.238605664420586</v>
       </c>
       <c r="C174">
-        <v>0.06559279031181386</v>
+        <v>-0.6743234986631209</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>-0.4893742883945957</v>
+        <v>0.5494677362175866</v>
       </c>
       <c r="C175">
-        <v>0.6636535867902751</v>
+        <v>0.2712881233055517</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>1.617441426092165</v>
+        <v>-0.05275632481746725</v>
       </c>
       <c r="C176">
-        <v>-0.04080489510396923</v>
+        <v>0.5728689726437221</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>-1.267634353256074</v>
+        <v>-0.5534705350683491</v>
       </c>
       <c r="C177">
-        <v>-0.9675982209226592</v>
+        <v>-1.651711581121083</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>-0.133607669154043</v>
+        <v>0.01690998098081451</v>
       </c>
       <c r="C178">
-        <v>0.5155276760989798</v>
+        <v>-0.01178339202355501</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>-0.810433812051366</v>
+        <v>-1.183518660851673</v>
       </c>
       <c r="C179">
-        <v>-1.326875257379938</v>
+        <v>-0.2632967576338853</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>0.4147941191432828</v>
+        <v>0.637287719558823</v>
       </c>
       <c r="C180">
-        <v>-1.428071056277028</v>
+        <v>-0.4882825503656295</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>0.08028434963356443</v>
+        <v>0.6918692255019442</v>
       </c>
       <c r="C181">
-        <v>-0.6185867162366869</v>
+        <v>-0.906873339787869</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>-0.2489643482115361</v>
+        <v>-0.9885007285972891</v>
       </c>
       <c r="C182">
-        <v>-2.126201957221123</v>
+        <v>-1.262518345409602</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>-0.9682760680354178</v>
+        <v>-0.1991853951717141</v>
       </c>
       <c r="C183">
-        <v>-1.135718489862307</v>
+        <v>0.6511702594664881</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>-0.2233038404681447</v>
+        <v>-0.972158041763028</v>
       </c>
       <c r="C184">
-        <v>-0.5664828270009776</v>
+        <v>0.3642936456384282</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>0.3404879687850189</v>
+        <v>1.091276602046121</v>
       </c>
       <c r="C185">
-        <v>-0.4443959643995066</v>
+        <v>0.2139004028873719</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>-1.628505701011002</v>
+        <v>0.7184124262350714</v>
       </c>
       <c r="C186">
-        <v>-1.534493139825171</v>
+        <v>1.206033965090632</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>-0.5574449281467244</v>
+        <v>-0.1505700843729906</v>
       </c>
       <c r="C187">
-        <v>-1.52891060899174</v>
+        <v>-0.9080913611713564</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>0.030623084300342</v>
+        <v>-0.6242841671737173</v>
       </c>
       <c r="C188">
-        <v>0.353877083083826</v>
+        <v>-0.7539882609729046</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>-1.165776440057997</v>
+        <v>0.2345428992094259</v>
       </c>
       <c r="C189">
-        <v>-0.4073238343355222</v>
+        <v>2.548508292270238</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>1.034167305195492</v>
+        <v>0.2926755289368731</v>
       </c>
       <c r="C190">
-        <v>0.6511063042217862</v>
+        <v>0.757012453498635</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>0.3627011294456198</v>
+        <v>-0.7268385950122881</v>
       </c>
       <c r="C191">
-        <v>-0.589358008105992</v>
+        <v>0.06257642214654047</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>0.5793301297632071</v>
+        <v>1.191418478987422</v>
       </c>
       <c r="C192">
-        <v>0.2594199921273246</v>
+        <v>-0.4717152643042898</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>-0.8678864548908397</v>
+        <v>1.880172544040374</v>
       </c>
       <c r="C193">
-        <v>1.603591857999358</v>
+        <v>2.500704440425477</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>-0.5361959054403248</v>
+        <v>-0.3406622310257221</v>
       </c>
       <c r="C194">
-        <v>-1.475798801885463</v>
+        <v>-0.9215490734086427</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>-0.2002338118881635</v>
+        <v>-0.3732525382398834</v>
       </c>
       <c r="C195">
-        <v>0.7995278735308132</v>
+        <v>0.4590971338517103</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>0.1775408332522883</v>
+        <v>-1.448522085938339</v>
       </c>
       <c r="C196">
-        <v>0.04815167957603425</v>
+        <v>-0.6003912276353939</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>-1.450400197233646</v>
+        <v>1.34164560119785</v>
       </c>
       <c r="C197">
-        <v>0.6543047403573602</v>
+        <v>-0.3683735960017457</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>0.7082474069535943</v>
+        <v>-0.29325769201635</v>
       </c>
       <c r="C198">
-        <v>0.2727380130687356</v>
+        <v>1.511868307760133</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>-1.481358200705915</v>
+        <v>-2.316188654486118</v>
       </c>
       <c r="C199">
-        <v>-2.181820672109874</v>
+        <v>-1.397965638362257</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>0.1502657557365119</v>
+        <v>-0.5421492336144379</v>
       </c>
       <c r="C200">
-        <v>-0.1818756491400251</v>
+        <v>-0.03256328966190875</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>-0.6151656058895603</v>
+        <v>-0.07601701796400021</v>
       </c>
       <c r="C201">
-        <v>-0.02763295800569754</v>
+        <v>0.4037430436202921</v>
       </c>
     </row>
   </sheetData>
